--- a/Test_Cases/05_Player/TCE_Player_Test_Cases.xlsx
+++ b/Test_Cases/05_Player/TCE_Player_Test_Cases.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$K$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,20 +432,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="78" customWidth="1" min="9" max="9"/>
-    <col width="78" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="84" customWidth="1" min="8" max="8"/>
+    <col width="82" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1094,8 +1094,505 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC-TCE-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Verify each supported TCE resource type opens in TCE Player</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Type coverage</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Playlist contains each supported TCE type.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>TCE video; Lecture note; Interactivity; Game; Tool</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1. Open each resource type from Playlist one at a time.
+2. Observe the player used.
+3. Repeat for all five types.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>TCE video, Lecture note, Interactivity, Game and Tool all open in the TCE Player.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Each resource is open in the correct player.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TC-TCE-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Verify TCE content is interactive after loading</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Content interaction</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>TCE resource has loaded.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Interactive TCE content</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1. Open TCE resource.
+2. Wait for content to finish loading.
+3. Use controls inside the content.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Content controls respond and the content is usable.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Content remains active.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC-TCE-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Verify TCE loading spinner clears after content loads</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Valid TCE package available.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>TCE resource</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1. Open TCE resource.
+2. Observe spinner while loading.
+3. Wait until package loads.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Spinner is displayed during loading and disappears when content is available.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Loaded content is displayed.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TC-TCE-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Verify TCE player handles slow loading without appearing permanently stuck</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Slow loading</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Negative / Performance</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>A TCE package can be loaded with delayed response.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Delayed TCE package</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1. Open delayed TCE resource.
+2. Observe loading state.
+3. Wait for the package to complete.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Player continues loading and does not remain indefinitely stuck when the package eventually completes.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Content loads or fails visibly.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC-TCE-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Verify Pan tool prevents interaction with TCE content</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Pan interaction</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>TCE content is open.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>TCE resource</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1. Open TCE.
+2. Select Pan tool.
+3. Tap/drag over content.
+4. Select another tool.
+5. Tap content again.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>With Pan selected, content stops taking taps so the board can be dragged; another tool restores content interaction.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>TCE interaction matches selected tool.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TC-TCE-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Verify TCE audio stops when player is closed</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Audio cleanup</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>TCE resource with audio is playing.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>TCE audio content</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1. Open TCE content with audio.
+2. Start audio.
+3. Close player.
+4. Observe audio.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Audio/activity stops immediately after closing.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>No TCE audio continues.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TC-TCE-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Verify opening the same TCE resource again pans to existing player</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate prevention</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>TCE resource is already open.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Same TCE resource</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1. Open TCE resource.
+2. Pan board elsewhere.
+3. Tap same resource again.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Existing TCE player is reused and board pans back to it; no second copy opens.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Only one copy remains.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TC-TCE-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Verify different TCE resources can remain open together</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Multiple players</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>At least two different TCE resources exist.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Two TCE types</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1. Open TCE resource A.
+2. Open TCE resource B.
+3. Observe both.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Both resources remain open without disturbing each other.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Both players remain available.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TC-TCE-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Verify failed TCE package shows a visible failure</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Failure</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>A missing/corrupt TCE package can be used.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Missing/corrupt package</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1. Open failing TCE resource.
+2. Observe player after load attempt.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Failure is visible; an empty player or permanent spinner is not left silently.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Failure state is displayed.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1106,17 +1603,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1381,8 +1878,206 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC-TCE-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Verify each supported TCE resource type opens in TCE Player</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC-TCE-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Verify TCE content is interactive after loading</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC-TCE-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Verify TCE loading spinner clears after content loads</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC-TCE-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Verify TCE player handles slow loading without appearing permanently stuck</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC-TCE-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Verify Pan tool prevents interaction with TCE content</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC-TCE-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Verify TCE audio stops when player is closed</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC-TCE-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Verify opening the same TCE resource again pans to existing player</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC-TCE-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Verify different TCE resources can remain open together</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC-TCE-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Verify failed TCE package shows a visible failure</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>